--- a/survey_templates/038_family_medicine_residency_program_graduate_survey--survey_templates.xlsx
+++ b/survey_templates/038_family_medicine_residency_program_graduate_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -575,7 +575,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Education</t>
+          <t>Education Rating</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -621,7 +621,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Clinical Exposure</t>
+          <t>Clinical Exposure Rating</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -667,7 +667,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Program Flexibility</t>
+          <t>Program Flexibility Rating</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -800,7 +800,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>program_rating</t>
+          <t>program_rating_2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -892,12 +892,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>education_rating</t>
+          <t>education_rating_2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Education</t>
+          <t>Education Rating 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -966,7 +966,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Education</t>
+          <t>Education (4)</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -1125,7 +1125,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C43"/>
+  <dimension ref="A1:C39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -1209,12 +1209,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Very satisfied</t>
         </is>
       </c>
     </row>
@@ -1226,12 +1226,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -1243,46 +1243,46 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>dissatisfied</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Dissatisfied</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>clinical_exposure_rating_choices</t>
+          <t>program_flexibility_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>clinical_exposure_rating_choices</t>
+          <t>program_flexibility_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>moderate</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>Moderate</t>
         </is>
       </c>
     </row>
@@ -1294,46 +1294,46 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>program_flexibility_choices</t>
+          <t>program_flexibility_rating_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>moderate</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>Very satisfied</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>program_flexibility_choices</t>
+          <t>program_flexibility_rating_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -1345,172 +1345,172 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>dissatisfied</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Dissatisfied</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>program_flexibility_rating_choices</t>
+          <t>education_fundamentals_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>strengths</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Strengths</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>program_flexibility_rating_choices</t>
+          <t>education_fundamentals_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>weaknesses</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Weaknesses</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>program_flexibility_rating_choices</t>
+          <t>overall_experience_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>positive</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>Positive</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>program_flexibility_rating_choices</t>
+          <t>overall_experience_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>negative</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>Negative</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>education_fundamentals_choices</t>
+          <t>program_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>strengths</t>
+          <t>family_medicine_residency_program</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Strengths</t>
+          <t>Family Medicine Residency Program</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>education_fundamentals_choices</t>
+          <t>program_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>weaknesses</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Weaknesses</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>overall_experience_choices</t>
+          <t>education_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>positive</t>
+          <t>md/phd</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>MD/PhD</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>overall_experience_choices</t>
+          <t>education_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>negative</t>
+          <t>do</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>DO</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>program_choices</t>
+          <t>education_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>family_medicine_residency_program</t>
+          <t>dnp</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Family Medicine Residency Program</t>
+          <t>DNP</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>program_choices</t>
+          <t>education_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1527,102 +1527,102 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>education_choices</t>
+          <t>gender_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>md/phd</t>
+          <t>male</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>MD/PhD</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>education_choices</t>
+          <t>gender_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>do</t>
+          <t>female</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>DO</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>education_choices</t>
+          <t>ethnicity_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>dnp</t>
+          <t>white</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>DNP</t>
+          <t>White</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>education_choices</t>
+          <t>ethnicity_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>black_or_african_american</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Black or African American</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>gender_choices</t>
+          <t>ethnicity_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>asian_or_pacific_islander</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Asian or Pacific Islander</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>gender_choices</t>
+          <t>ethnicity_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>hispanic_or_latino</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Hispanic or Latino</t>
         </is>
       </c>
     </row>
@@ -1634,80 +1634,80 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>white</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>White</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>ethnicity_choices</t>
+          <t>race_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>black_or_african_american</t>
+          <t>white</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Black or African American</t>
+          <t>White</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>ethnicity_choices</t>
+          <t>race_choices</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>asian_or_pacific_islander</t>
+          <t>black_or_african_american</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Asian or Pacific Islander</t>
+          <t>Black or African American</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>ethnicity_choices</t>
+          <t>race_choices</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>hispanic_or_latino</t>
+          <t>asian_or_pacific_islander</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Hispanic or Latino</t>
+          <t>Asian or Pacific Islander</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>ethnicity_choices</t>
+          <t>race_choices</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>hispanic_or_latino</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Hispanic or Latino</t>
         </is>
       </c>
     </row>
@@ -1719,146 +1719,78 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>white</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>White</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>race_choices</t>
+          <t>employment_status_choices</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>black_or_african_american</t>
+          <t>employed</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Black or African American</t>
+          <t>Employed</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>race_choices</t>
+          <t>employment_status_choices</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>asian_or_pacific_islander</t>
+          <t>unemployed</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Asian or Pacific Islander</t>
+          <t>Unemployed</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>race_choices</t>
+          <t>employment_status_choices</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>hispanic_or_latino</t>
+          <t>retired</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Hispanic or Latino</t>
+          <t>Retired</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>race_choices</t>
+          <t>employment_status_choices</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>student</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>employment_status_choices</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>employed</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Employed</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>employment_status_choices</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>unemployed</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Unemployed</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>employment_status_choices</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>retired</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Retired</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>employment_status_choices</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>student</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
         <is>
           <t>Student</t>
         </is>
